--- a/marketing/배포기록표.xlsx
+++ b/marketing/배포기록표.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="98">
   <si>
     <t xml:space="preserve">게릴라 배포 실험 — 요약</t>
   </si>
@@ -383,6 +383,245 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">차 배포</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">채널별 — 어느 경로로 들어오는가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">유입경로</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">성사율 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">문의 대비</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">QR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">문자</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">전화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">카톡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인스타</t>
+  </si>
+  <si>
+    <t xml:space="preserve">네이버</t>
+  </si>
+  <si>
+    <t xml:space="preserve">당근</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기타</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 성사율의 분모는 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">문의 수</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위 두 블록의 전환율</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분모</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배포 대수</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과 다른 지표이니 섞어서 비교하지 마세요</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
   </si>
   <si>
@@ -1033,9 +1272,6 @@
     <t xml:space="preserve">연락처</t>
   </si>
   <si>
-    <t xml:space="preserve">유입경로</t>
-  </si>
-  <si>
     <t xml:space="preserve">첫 방문일</t>
   </si>
   <si>
@@ -1048,9 +1284,6 @@
     <t xml:space="preserve">2026-08-12</t>
   </si>
   <si>
-    <t xml:space="preserve">예시</t>
-  </si>
-  <si>
     <t xml:space="preserve">김○○</t>
   </si>
   <si>
@@ -1094,7 +1327,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">← 예시 행입니다</t>
+      <t xml:space="preserve">← 예시 행</t>
     </r>
     <r>
       <rPr>
@@ -1115,7 +1348,104 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">코드가 </t>
+      <t xml:space="preserve">집계 범위</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(5</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">행부터</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">밖이라 숫자에 잡히지 않습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">덮어쓰거나 지우세요</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">※ '</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구독 전환</t>
     </r>
     <r>
       <rPr>
@@ -1136,13 +1466,183 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">예시</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF6B7A8C"/>
+      <t xml:space="preserve">에 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Y</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">를 넣는 순간 배포기록</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요약의 전환율이 함께 움직입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF6B7A8C"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">쓰는 법</t>
+  </si>
+  <si>
+    <t xml:space="preserve">색 규칙</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노란 칸 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파란 글씨</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직접 입력하는 곳</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이것만 채우면 됩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">검은 글씨</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수식이 계산합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건드리면 집계가 깨집니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">순서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 배포 당일</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1151,19 +1651,83 @@
     </r>
     <r>
       <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF6B7A8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">라 집계에 잡히지 않습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF6B7A8C"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배포기록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 단지명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배포일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배포 대수를 적습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차에서 바로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1172,22 +1736,94 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF6B7A8C"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">※ '</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF6B7A8C"/>
+    <t xml:space="preserve">② 문의가 올 때</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">문의접수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 한 줄 추가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">코드는 목록에서 고릅니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">③ 구독이 성사되면</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그 행의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -1195,9 +1831,7 @@
     </r>
     <r>
       <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF6B7A8C"/>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1206,19 +1840,15 @@
     </r>
     <r>
       <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF6B7A8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF6B7A8C"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">을 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1227,40 +1857,32 @@
     </r>
     <r>
       <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF6B7A8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">를 넣는 순간 배포기록</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF6B7A8C"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF6B7A8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">요약의 전환율이 함께 움직입니다</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF6B7A8C"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 바꿉니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">나머지는 자동입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1269,31 +1891,221 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">쓰는 법</t>
-  </si>
-  <si>
-    <t xml:space="preserve">색 규칙</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">노란 칸 </t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">④ 4</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주 후</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 판정을 봅니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">집중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 뜬 단지에 자원을 몰아넣습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">코드 읽는 법</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WJ=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">운정 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· A=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단지 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· 1=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배포 회차</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">주의</t>
+  </si>
+  <si>
+    <t xml:space="preserve">배포 대수를 빠뜨리지 마세요</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">문의 수는 분자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배포 대수는 분모입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분모가 없으면 전환율이 안 나오고 실험 전체가 무의미해집니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -1301,17 +2113,53 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">파란 글씨</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">직접 입력하는 곳</t>
+      <t xml:space="preserve">문의접수 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">행은 예시입니다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">집계는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">행부터입니다</t>
     </r>
     <r>
       <rPr>
@@ -1328,618 +2176,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">이것만 채우면 됩니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">검은 글씨</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">수식이 계산합니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건드리면 집계가 깨집니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">순서</t>
-  </si>
-  <si>
-    <t xml:space="preserve">① 배포 당일</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">배포기록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 단지명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">배포일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">배포 대수를 적습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">차에서 바로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">② 문의가 올 때</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">문의접수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 한 줄 추가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">코드는 목록에서 고릅니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">③ 구독이 성사되면</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그 행의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구독 전환</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">을 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 바꿉니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">나머지는 자동입니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">④ 4</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주 후</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">요약</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 판정을 봅니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. '</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">집중</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이 뜬 단지에 자원을 몰아넣습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">코드 읽는 법</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">WJ=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">운정 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· A=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단지 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· 1=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">배포 회차</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">주의</t>
-  </si>
-  <si>
-    <t xml:space="preserve">배포 대수를 빠뜨리지 마세요</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">문의 수는 분자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">배포 대수는 분모입니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">분모가 없으면 전환율이 안 나오고 실험 전체가 무의미해집니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">문의접수 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">행은 예시입니다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">코드가 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">예시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">라 집계에 잡히지 않습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지우셔도 됩니다</t>
+      <t xml:space="preserve">덮어쓰거나 지우셔도 됩니다</t>
     </r>
     <r>
       <rPr>
@@ -2063,7 +2300,7 @@
     <numFmt numFmtId="167" formatCode="#,##0\원"/>
     <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2145,6 +2382,14 @@
       <sz val="10"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -2307,7 +2552,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2315,7 +2560,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2323,7 +2568,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2343,7 +2588,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2379,7 +2624,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2635,7 +2880,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -2901,60 +3146,220 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="12" t="n">
-        <f aca="false">배포기록!D13</f>
-        <v>0</v>
+      <c r="B21" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="12" t="n">
-        <f aca="false">배포기록!E13</f>
-        <v>0</v>
+      <c r="A22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="8" t="n">
+        <f aca="false">COUNTIFS(문의접수!$E$5:$E$503,$A22)</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <f aca="false">COUNTIFS(문의접수!$E$5:$E$503,$A22,문의접수!$F$5:$F$503,"Y")</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="9" t="str">
+        <f aca="false">IFERROR(C22/B22,"")</f>
+        <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="12" t="n">
-        <f aca="false">배포기록!F13</f>
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="B23" s="8" t="n">
+        <f aca="false">COUNTIFS(문의접수!$E$5:$E$503,$A23)</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <f aca="false">COUNTIFS(문의접수!$E$5:$E$503,$A23,문의접수!$F$5:$F$503,"Y")</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="9" t="str">
+        <f aca="false">IFERROR(C23/B23,"")</f>
+        <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="14" t="str">
-        <f aca="false">IFERROR(B23/B21,"")</f>
+      <c r="A24" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="8" t="n">
+        <f aca="false">COUNTIFS(문의접수!$E$5:$E$503,$A24)</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <f aca="false">COUNTIFS(문의접수!$E$5:$E$503,$A24,문의접수!$F$5:$F$503,"Y")</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="9" t="str">
+        <f aca="false">IFERROR(C24/B24,"")</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="15" t="n">
-        <f aca="false">B23*80000</f>
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="B25" s="8" t="n">
+        <f aca="false">COUNTIFS(문의접수!$E$5:$E$503,$A25)</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <f aca="false">COUNTIFS(문의접수!$E$5:$E$503,$A25,문의접수!$F$5:$F$503,"Y")</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="9" t="str">
+        <f aca="false">IFERROR(C25/B25,"")</f>
+        <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="16" t="str">
-        <f aca="false">IF(SUM(B21)=0,"데이터 없음",INDEX($A$8:$A$10,MATCH(MAX($F$8:$F$10),$F$8:$F$10,0)))</f>
+      <c r="A26" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="8" t="n">
+        <f aca="false">COUNTIFS(문의접수!$E$5:$E$503,$A26)</f>
+        <v>0</v>
+      </c>
+      <c r="C26" s="8" t="n">
+        <f aca="false">COUNTIFS(문의접수!$E$5:$E$503,$A26,문의접수!$F$5:$F$503,"Y")</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="9" t="str">
+        <f aca="false">IFERROR(C26/B26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="8" t="n">
+        <f aca="false">COUNTIFS(문의접수!$E$5:$E$503,$A27)</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <f aca="false">COUNTIFS(문의접수!$E$5:$E$503,$A27,문의접수!$F$5:$F$503,"Y")</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="9" t="str">
+        <f aca="false">IFERROR(C27/B27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="8" t="n">
+        <f aca="false">COUNTIFS(문의접수!$E$5:$E$503,$A28)</f>
+        <v>0</v>
+      </c>
+      <c r="C28" s="8" t="n">
+        <f aca="false">COUNTIFS(문의접수!$E$5:$E$503,$A28,문의접수!$F$5:$F$503,"Y")</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="9" t="str">
+        <f aca="false">IFERROR(C28/B28,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="8" t="n">
+        <f aca="false">COUNTIFS(문의접수!$E$5:$E$503,$A29)</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="8" t="n">
+        <f aca="false">COUNTIFS(문의접수!$E$5:$E$503,$A29,문의접수!$F$5:$F$503,"Y")</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="9" t="str">
+        <f aca="false">IFERROR(C29/B29,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="12" t="n">
+        <f aca="false">배포기록!D13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="12" t="n">
+        <f aca="false">배포기록!E13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="12" t="n">
+        <f aca="false">배포기록!F13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="14" t="str">
+        <f aca="false">IFERROR(B36/B34,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="15" t="n">
+        <f aca="false">B36*80000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="16" t="str">
+        <f aca="false">IF(SUM(B34)=0,"데이터 없음",INDEX($A$8:$A$10,MATCH(MAX($F$8:$F$10),$F$8:$F$10,0)))</f>
         <v>데이터 없음</v>
       </c>
-      <c r="C26" s="17" t="s">
-        <v>26</v>
+      <c r="C39" s="17" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2988,23 +3393,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>6</v>
@@ -3025,25 +3430,25 @@
         <v>11</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="20"/>
       <c r="D4" s="21"/>
       <c r="E4" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A4)</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A4)</f>
         <v>0</v>
       </c>
       <c r="F4" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A4,문의접수!$F$4:$F$503,"Y")</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A4,문의접수!$F$5:$F$503,"Y")</f>
         <v>0</v>
       </c>
       <c r="G4" s="9" t="str">
@@ -3069,17 +3474,17 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="20"/>
       <c r="D5" s="21"/>
       <c r="E5" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A5)</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A5)</f>
         <v>0</v>
       </c>
       <c r="F5" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A5,문의접수!$F$4:$F$503,"Y")</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A5,문의접수!$F$5:$F$503,"Y")</f>
         <v>0</v>
       </c>
       <c r="G5" s="9" t="str">
@@ -3105,17 +3510,17 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="20"/>
       <c r="D6" s="21"/>
       <c r="E6" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A6)</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A6)</f>
         <v>0</v>
       </c>
       <c r="F6" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A6,문의접수!$F$4:$F$503,"Y")</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A6,문의접수!$F$5:$F$503,"Y")</f>
         <v>0</v>
       </c>
       <c r="G6" s="9" t="str">
@@ -3141,17 +3546,17 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="20"/>
       <c r="D7" s="21"/>
       <c r="E7" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A7)</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A7)</f>
         <v>0</v>
       </c>
       <c r="F7" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A7,문의접수!$F$4:$F$503,"Y")</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A7,문의접수!$F$5:$F$503,"Y")</f>
         <v>0</v>
       </c>
       <c r="G7" s="9" t="str">
@@ -3177,17 +3582,17 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="20"/>
       <c r="D8" s="21"/>
       <c r="E8" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A8)</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A8)</f>
         <v>0</v>
       </c>
       <c r="F8" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A8,문의접수!$F$4:$F$503,"Y")</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A8,문의접수!$F$5:$F$503,"Y")</f>
         <v>0</v>
       </c>
       <c r="G8" s="9" t="str">
@@ -3213,17 +3618,17 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="20"/>
       <c r="D9" s="21"/>
       <c r="E9" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A9)</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A9)</f>
         <v>0</v>
       </c>
       <c r="F9" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A9,문의접수!$F$4:$F$503,"Y")</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A9,문의접수!$F$5:$F$503,"Y")</f>
         <v>0</v>
       </c>
       <c r="G9" s="9" t="str">
@@ -3249,17 +3654,17 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="20"/>
       <c r="D10" s="21"/>
       <c r="E10" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A10)</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A10)</f>
         <v>0</v>
       </c>
       <c r="F10" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A10,문의접수!$F$4:$F$503,"Y")</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A10,문의접수!$F$5:$F$503,"Y")</f>
         <v>0</v>
       </c>
       <c r="G10" s="9" t="str">
@@ -3285,17 +3690,17 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
       <c r="D11" s="21"/>
       <c r="E11" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A11)</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A11)</f>
         <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A11,문의접수!$F$4:$F$503,"Y")</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A11,문의접수!$F$5:$F$503,"Y")</f>
         <v>0</v>
       </c>
       <c r="G11" s="9" t="str">
@@ -3321,17 +3726,17 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="20"/>
       <c r="D12" s="21"/>
       <c r="E12" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A12)</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A12)</f>
         <v>0</v>
       </c>
       <c r="F12" s="8" t="n">
-        <f aca="false">COUNTIFS(문의접수!$B$4:$B$503,$A12,문의접수!$F$4:$F$503,"Y")</f>
+        <f aca="false">COUNTIFS(문의접수!$B$5:$B$503,$A12,문의접수!$F$5:$F$503,"Y")</f>
         <v>0</v>
       </c>
       <c r="G12" s="9" t="str">
@@ -3357,7 +3762,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
@@ -3387,12 +3792,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3411,7 +3816,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3425,70 +3830,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>56</v>
+        <v>66</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H4" s="26" t="n">
         <v>80000</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3920,9 +4325,20 @@
       <c r="H43" s="29"/>
       <c r="I43" s="28"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="17" t="s">
-        <v>63</v>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="27"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="28"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="17" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -3932,7 +4348,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:E503" type="list">
-      <formula1>"QR문자,전화,카톡,대면,기타"</formula1>
+      <formula1>"QR문자,전화,카톡,대면,인스타,네이버,당근,기타"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F503" type="list">
@@ -3964,7 +4380,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3973,23 +4389,23 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3998,39 +4414,39 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4039,15 +4455,15 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4056,31 +4472,31 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
